--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484123_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484123_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1894</v>
+        <v>3.0016</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1718</v>
+        <v>2.8061</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0176</v>
+        <v>0.1955</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.2162</v>
+        <v>2.5504</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2821</v>
+        <v>0.1458</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9342</v>
+        <v>2.4046</v>
       </c>
       <c r="J2" t="n">
-        <v>0.743</v>
+        <v>3.6343</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2538</v>
+        <v>2.344</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.5108</v>
+        <v>1.2903</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9592</v>
+        <v>-1.0839</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.5359</v>
+        <v>-2.1982</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5767</v>
+        <v>1.1143</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9919</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2652</v>
+        <v>-0.1601</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0115</v>
+        <v>0.1475</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2767</v>
+        <v>-0.3076</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6789</v>
+        <v>1.2065</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6076</v>
+        <v>1.2065</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1874</v>
+        <v>2.7919</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1882</v>
+        <v>2.3815</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0009</v>
+        <v>0.4103</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5504</v>
+        <v>-1.2162</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1458</v>
+        <v>-0.2821</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4046</v>
+        <v>-0.9342</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6343</v>
+        <v>0.743</v>
       </c>
       <c r="K3" t="n">
-        <v>2.344</v>
+        <v>2.2538</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2903</v>
+        <v>-1.5108</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0839</v>
+        <v>-1.9592</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1982</v>
+        <v>-2.5359</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1143</v>
+        <v>0.5767</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9743000000000001</v>
+        <v>0.3373</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4703</v>
+        <v>0.2212</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.504</v>
+        <v>0.1161</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2065</v>
+        <v>2.6789</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>2.6076</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9141</v>
+        <v>2.2188</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0914</v>
+        <v>3.2558</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1773</v>
+        <v>-1.037</v>
       </c>
       <c r="G4" t="n">
         <v>-1.7539</v>
@@ -766,13 +766,13 @@
         <v>0.3968</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0822</v>
+        <v>0.2225</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1757</v>
+        <v>-0.0113</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0935</v>
+        <v>0.2338</v>
       </c>
       <c r="V4" t="n">
         <v>3.3534</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8768</v>
+        <v>1.0069</v>
       </c>
       <c r="E5" t="n">
-        <v>0.735</v>
+        <v>0.8371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1418</v>
+        <v>0.1699</v>
       </c>
       <c r="G5" t="n">
         <v>0.1108</v>
@@ -844,13 +844,13 @@
         <v>0.7935</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.242</v>
+        <v>-0.1119</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1247</v>
+        <v>-0.0227</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V5" t="n">
         <v>1.2065</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1154</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7197</v>
+        <v>2.1151</v>
       </c>
       <c r="F6" t="n">
-        <v>1.835</v>
+        <v>-2.0179</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4462</v>
+        <v>0.5483</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2895</v>
+        <v>-1.2046</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1567</v>
+        <v>1.753</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.08690000000000001</v>
+        <v>2.9992</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5104</v>
+        <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5973000000000001</v>
+        <v>2.5302</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3593</v>
+        <v>-2.4508</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7999</v>
+        <v>-1.6736</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4406</v>
+        <v>-0.7772</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9782</v>
+        <v>0.1601</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0258</v>
+        <v>0.1078</v>
       </c>
       <c r="U6" t="n">
-        <v>2.004</v>
+        <v>0.0524</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4085</v>
+        <v>-1.2065</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. DE LEON</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0273</v>
+        <v>0.0752</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.15</v>
+        <v>-0.6937</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1227</v>
+        <v>0.7689</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5725</v>
+        <v>-1.4462</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7361</v>
+        <v>-1.2895</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1635</v>
+        <v>-0.1567</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2788</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0017</v>
+        <v>0.5104</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7229</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2937</v>
+        <v>-1.3593</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7343</v>
+        <v>-1.7999</v>
       </c>
       <c r="O7" t="n">
         <v>0.4406</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1741</v>
+        <v>-0.1984</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0684</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2391</v>
+        <v>0.0001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1707</v>
+        <v>0.9379</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0639</v>
+        <v>-0.4085</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0639</v>
+        <v>-0.4085</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>R. DE LEON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7278</v>
+        <v>-1.2639</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5426</v>
+        <v>-1.4707</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2704</v>
+        <v>0.2068</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5483</v>
+        <v>-1.5725</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2046</v>
+        <v>-2.7361</v>
       </c>
       <c r="I8" t="n">
-        <v>1.753</v>
+        <v>1.1635</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9992</v>
+        <v>-0.2788</v>
       </c>
       <c r="K8" t="n">
-        <v>0.469</v>
+        <v>-1.0017</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5302</v>
+        <v>0.7229</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4508</v>
+        <v>-1.2937</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6736</v>
+        <v>-1.7343</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7772</v>
+        <v>0.4406</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5952</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R8" t="n">
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6649</v>
+        <v>0.8318</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4647</v>
+        <v>0.9184</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2001</v>
+        <v>-0.0866</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2065</v>
+        <v>1.0639</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0639</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3296</v>
+        <v>-2.8326</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6784</v>
+        <v>-0.3497</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6512</v>
+        <v>-2.4829</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5302</v>
@@ -1156,13 +1156,13 @@
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7833</v>
+        <v>-0.2862</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3514</v>
+        <v>-0.0226</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4319</v>
+        <v>-0.2636</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6032</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3461</v>
+        <v>-2.9425</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8451</v>
+        <v>-1.3294</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.501</v>
+        <v>-1.6132</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2405</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4943</v>
+        <v>-0.0907</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2323</v>
+        <v>0.2835</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.262</v>
+        <v>-0.3742</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8097</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8526</v>
+        <v>-4.2826</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.84</v>
+        <v>-1.1858</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0127</v>
+        <v>-3.0968</v>
       </c>
       <c r="G11" t="n">
         <v>-2.531</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8848</v>
+        <v>0.4549</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1418</v>
+        <v>-0.204</v>
       </c>
       <c r="U11" t="n">
-        <v>0.743</v>
+        <v>0.6589</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8097</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.000300000000001</v>
+        <v>-2.13</v>
       </c>
       <c r="E12" t="n">
-        <v>4.495800000000001</v>
+        <v>6.366300000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-8.4964</v>
@@ -1357,7 +1357,7 @@
         <v>-10.081</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.138</v>
+        <v>-8.137999999999998</v>
       </c>
       <c r="I12" t="n">
         <v>-1.9431</v>
@@ -1390,13 +1390,13 @@
         <v>13.887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4251999999999997</v>
+        <v>2.2957</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4525</v>
+        <v>1.4179</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8777999999999998</v>
+        <v>0.8778</v>
       </c>
       <c r="V12" t="n">
         <v>3.6716</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.841900000000001</v>
+        <v>9.5511</v>
       </c>
       <c r="E13" t="n">
-        <v>7.1067</v>
+        <v>8.025</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7352</v>
+        <v>1.5261</v>
       </c>
       <c r="G13" t="n">
         <v>5.8799</v>
@@ -1468,13 +1468,13 @@
         <v>1.9838</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4626</v>
+        <v>0.2465</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4963</v>
+        <v>-0.578</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0337</v>
+        <v>0.8246</v>
       </c>
       <c r="V13" t="n">
         <v>3.4247</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6165</v>
+        <v>6.5832</v>
       </c>
       <c r="E14" t="n">
-        <v>7.7755</v>
+        <v>8.0816</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.159</v>
+        <v>-1.4984</v>
       </c>
       <c r="G14" t="n">
         <v>7.3287</v>
@@ -1546,13 +1546,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6285</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0485</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.58</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4724</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3681</v>
+        <v>1.574</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2472</v>
+        <v>0.1249</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1209</v>
+        <v>1.4491</v>
       </c>
       <c r="G15" t="n">
         <v>-0.709</v>
@@ -1624,13 +1624,13 @@
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>1.942</v>
+        <v>1.1478</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8479</v>
+        <v>0.7256</v>
       </c>
       <c r="U15" t="n">
-        <v>0.094</v>
+        <v>0.4222</v>
       </c>
       <c r="V15" t="n">
         <v>1.1352</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2297</v>
+        <v>0.4295</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1078</v>
+        <v>0.3119</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1219</v>
+        <v>0.1177</v>
       </c>
       <c r="G16" t="n">
         <v>0.431</v>
@@ -1702,13 +1702,13 @@
         <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1955</v>
+        <v>0.3953</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0113</v>
+        <v>0.2154</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1842</v>
+        <v>0.1799</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>P. MAJORAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1872</v>
+        <v>-0.4042</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6285</v>
+        <v>-0.6353</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4413</v>
+        <v>0.2311</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2542</v>
+        <v>0.3162</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6999</v>
+        <v>-1.3459</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4457</v>
+        <v>1.6622</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1544</v>
+        <v>0.3509</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5444</v>
+        <v>-0.2165</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6101</v>
+        <v>0.5674</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9002</v>
+        <v>-0.0347</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1556</v>
+        <v>-1.1295</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0558</v>
+        <v>1.0948</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8463000000000001</v>
+        <v>0.486</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7991</v>
+        <v>0.0057</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0471</v>
+        <v>0.4803</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2322</v>
+        <v>-0.6371</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2201</v>
+        <v>-1.3224</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0121</v>
+        <v>0.6853</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0378</v>
+        <v>0.2542</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1815</v>
+        <v>0.6999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.4457</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6758</v>
+        <v>1.1544</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.5444</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>0.6101</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3621</v>
+        <v>-0.9002</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4542</v>
+        <v>0.1556</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8162</v>
+        <v>-1.0558</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7855</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5911</v>
+        <v>-0.2962</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4171</v>
+        <v>-0.4931</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1739</v>
+        <v>0.1969</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MAJORAL DE LOS RIOS</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5528</v>
+        <v>-1.4504</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4515</v>
+        <v>0.3523</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1013</v>
+        <v>-1.8027</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3162</v>
+        <v>0.2649</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3459</v>
+        <v>1.058</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6622</v>
+        <v>-0.793</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3509</v>
+        <v>0.4882</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2165</v>
+        <v>1.4368</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5674</v>
+        <v>-0.9486</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0347</v>
+        <v>-0.2233</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1295</v>
+        <v>-0.3788</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0948</v>
+        <v>0.1555</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6626</v>
+        <v>-0.2267</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8105</v>
+        <v>-0.1359</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1479</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4774</v>
+        <v>-2.0425</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0462</v>
+        <v>-2.1384</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5236</v>
+        <v>0.0959</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2649</v>
+        <v>1.0378</v>
       </c>
       <c r="H20" t="n">
-        <v>1.058</v>
+        <v>0.1815</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.793</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4882</v>
+        <v>0.6758</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4368</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9486</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2233</v>
+        <v>0.3621</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3788</v>
+        <v>-0.4542</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1555</v>
+        <v>0.8162</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1903</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2538</v>
+        <v>0.7808</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.442</v>
+        <v>0.4989</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8118</v>
+        <v>0.2819</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.6789</v>
+        <v>-2.0757</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.6789</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1601</v>
+        <v>-2.3575</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0228</v>
+        <v>-0.7167</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1373</v>
+        <v>-1.6408</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9466</v>
@@ -2092,13 +2092,13 @@
         <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9556</v>
+        <v>-0.153</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5498</v>
+        <v>-0.2437</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4059</v>
+        <v>0.0906</v>
       </c>
       <c r="V21" t="n">
         <v>-0.266</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4461</v>
+        <v>-4.525</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4642</v>
+        <v>-3.5865</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9819</v>
+        <v>-0.9385</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7763</v>
@@ -2170,13 +2170,13 @@
         <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6557</v>
+        <v>0.5767</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9921</v>
+        <v>-0.1303</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6636</v>
+        <v>0.707</v>
       </c>
       <c r="V22" t="n">
         <v>-0.532</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.000400000000001</v>
+        <v>6.721099999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>8.496300000000002</v>
+        <v>8.496400000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.495900000000001</v>
+        <v>-1.7752</v>
       </c>
       <c r="G23" t="n">
         <v>10.0808</v>
@@ -2248,13 +2248,13 @@
         <v>11.903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4251</v>
+        <v>2.2954</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8777999999999995</v>
+        <v>-0.8777999999999998</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4525000000000002</v>
+        <v>3.1733</v>
       </c>
       <c r="V23" t="n">
         <v>-3.6716</v>
@@ -2263,7 +2263,7 @@
         <v>5.4813</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.152699999999999</v>
+        <v>-9.152700000000001</v>
       </c>
     </row>
   </sheetData>
